--- a/tests/base_template.xlsx
+++ b/tests/base_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mark/Documents/Postdoc/Development/cmccdb-data/tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA746E7E-EEFE-2B40-880B-590E3235D570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BB2C8C-E38E-C844-8093-2DC04D7877BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3360" yWindow="500" windowWidth="28140" windowHeight="21900" xr2:uid="{67C290E4-36C7-6141-BA54-B171370FD48C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
   <si>
     <t>REACTION</t>
   </si>
@@ -261,6 +261,12 @@
   </si>
   <si>
     <t>Details</t>
+  </si>
+  <si>
+    <t>#!      - valid unit types can be found in reaction.proto and shorthands can be found at https://github.com/Center-for-Mechanical-Control-of-Chem/cmccdb-schema/blob/cmcc/cmccdb_schema/units.py</t>
+  </si>
+  <si>
+    <t>#!     - units should be specified inline with the field name, in parentheses</t>
   </si>
 </sst>
 </file>
@@ -686,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8C7A012-DC9A-214C-8A2F-E48641012DAD}">
-  <dimension ref="A1:X68"/>
+  <dimension ref="A1:X70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="1"/>
@@ -1127,362 +1133,324 @@
       <c r="W15" s="6"/>
       <c r="X15" s="6"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:24" s="4" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+    </row>
+    <row r="17" spans="1:24" s="4" customFormat="1" ht="19" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="B17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="E18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>66</v>
-      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="5"/>
+        <v>2</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="L19" s="7">
-        <v>45924.535416666666</v>
-      </c>
-      <c r="M19" s="7"/>
+        <v>27</v>
+      </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
+      <c r="E20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
-        <v>5</v>
+        <v>72</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="5"/>
+      <c r="E21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>45</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L21" s="7">
+        <v>45924.535416666666</v>
+      </c>
+      <c r="M21" s="7"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="E22" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
-      <c r="R24" s="3"/>
-      <c r="S24" s="3"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
+      <c r="E24" s="1" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="1">
-        <v>25</v>
-      </c>
-      <c r="D25" s="1" t="b">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="1">
-        <v>25</v>
+        <v>7</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>100</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O25" s="1">
-        <v>60</v>
+        <v>7</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>22</v>
+        <v>3</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="B26" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="1">
-        <v>25</v>
-      </c>
-      <c r="D26" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H26" s="1">
-        <v>25</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1">
-        <v>100</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O26" s="1">
-        <v>90</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A26" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
@@ -1510,7 +1478,7 @@
         <v>15</v>
       </c>
       <c r="L27" s="1">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="M27" s="1">
         <v>100</v>
@@ -1519,13 +1487,22 @@
         <v>24</v>
       </c>
       <c r="O27" s="1">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="P27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="T27" s="1" t="s">
-        <v>42</v>
+      <c r="U27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="V27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
@@ -1545,13 +1522,13 @@
         <v>37</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H28" s="1">
         <v>25</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L28" s="1">
         <v>0</v>
@@ -1563,20 +1540,99 @@
         <v>24</v>
       </c>
       <c r="O28" s="1">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="N29" s="2"/>
-    </row>
-    <row r="43" spans="14:14" x14ac:dyDescent="0.2">
-      <c r="N43" s="2"/>
-    </row>
-    <row r="44" spans="14:14" x14ac:dyDescent="0.2">
-      <c r="N44" s="2"/>
+      <c r="B29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="1">
+        <v>25</v>
+      </c>
+      <c r="D29" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="1">
+        <v>25</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L29" s="1">
+        <v>99</v>
+      </c>
+      <c r="M29" s="1">
+        <v>100</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O29" s="1">
+        <v>110</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="1">
+        <v>25</v>
+      </c>
+      <c r="D30" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H30" s="1">
+        <v>25</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>100</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O30" s="1">
+        <v>110</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="N31" s="2"/>
     </row>
     <row r="45" spans="14:14" x14ac:dyDescent="0.2">
       <c r="N45" s="2"/>
@@ -1590,67 +1646,65 @@
     <row r="48" spans="14:14" x14ac:dyDescent="0.2">
       <c r="N48" s="2"/>
     </row>
-    <row r="49" spans="12:13" x14ac:dyDescent="0.2">
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-    </row>
-    <row r="50" spans="12:13" x14ac:dyDescent="0.2">
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-    </row>
-    <row r="51" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="12:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="2"/>
+    </row>
+    <row r="50" spans="12:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="2"/>
+    </row>
+    <row r="51" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
     </row>
-    <row r="52" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="52" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
     </row>
-    <row r="53" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
     </row>
-    <row r="54" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="54" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
     </row>
-    <row r="55" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
     </row>
-    <row r="56" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="56" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
     </row>
-    <row r="57" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="57" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
     </row>
-    <row r="58" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
     </row>
-    <row r="59" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="59" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
     </row>
-    <row r="60" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
     </row>
-    <row r="61" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="61" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
     </row>
-    <row r="62" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
     </row>
-    <row r="63" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
     </row>
-    <row r="64" spans="12:13" x14ac:dyDescent="0.2">
+    <row r="64" spans="12:14" x14ac:dyDescent="0.2">
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
     </row>
@@ -1670,10 +1724,18 @@
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
     </row>
+    <row r="69" spans="12:13" x14ac:dyDescent="0.2">
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+    </row>
+    <row r="70" spans="12:13" x14ac:dyDescent="0.2">
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C19" r:id="rId1" xr:uid="{9692DAF0-C3B8-7047-B3C8-43A515C64126}"/>
-    <hyperlink ref="K19" r:id="rId2" xr:uid="{444FA2CD-6367-4740-AF6F-F1485DC566E6}"/>
+    <hyperlink ref="C21" r:id="rId1" xr:uid="{9692DAF0-C3B8-7047-B3C8-43A515C64126}"/>
+    <hyperlink ref="K21" r:id="rId2" xr:uid="{444FA2CD-6367-4740-AF6F-F1485DC566E6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
